--- a/output/Data and Chart Outputs/ireland_gni_transparency_daily.xlsx
+++ b/output/Data and Chart Outputs/ireland_gni_transparency_daily.xlsx
@@ -20,9 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,13 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -157,7 +157,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Ireland gas entry flows (GNI) (to Sep/26)</a:t>
+              <a:t>Ireland gas entry flows (GNI) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -186,12 +186,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$183</f>
+              <f>'Chart'!$E$2:$E$186</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$183</f>
+              <f>'Chart'!$B$2:$B$186</f>
             </numRef>
           </val>
         </ser>
@@ -214,12 +214,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$183</f>
+              <f>'Chart'!$E$2:$E$186</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$183</f>
+              <f>'Chart'!$C$2:$C$186</f>
             </numRef>
           </val>
         </ser>
@@ -242,12 +242,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$183</f>
+              <f>'Chart'!$E$2:$E$186</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$183</f>
+              <f>'Chart'!$D$2:$D$186</f>
             </numRef>
           </val>
         </ser>
@@ -259,23 +259,63 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>GWh/day</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -305,7 +345,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Ireland gas consumption by market sector (GNI) (to Sep/26)</a:t>
+              <a:t>Ireland gas consumption by market sector (GNI) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -334,12 +374,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Consumption'!$E$2:$E$183</f>
+              <f>'Chart - Consumption'!$E$2:$E$186</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Consumption'!$B$2:$B$183</f>
+              <f>'Chart - Consumption'!$B$2:$B$186</f>
             </numRef>
           </val>
         </ser>
@@ -362,12 +402,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Consumption'!$E$2:$E$183</f>
+              <f>'Chart - Consumption'!$E$2:$E$186</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Consumption'!$C$2:$C$183</f>
+              <f>'Chart - Consumption'!$C$2:$C$186</f>
             </numRef>
           </val>
         </ser>
@@ -390,12 +430,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Consumption'!$E$2:$E$183</f>
+              <f>'Chart - Consumption'!$E$2:$E$186</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Consumption'!$D$2:$D$183</f>
+              <f>'Chart - Consumption'!$D$2:$D$186</f>
             </numRef>
           </val>
         </ser>
@@ -407,23 +447,63 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>GWh/day</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -811,6 +891,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -825,6 +906,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -839,6 +921,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -853,6 +936,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -878,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E183"/>
+  <dimension ref="A1:E186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -912,7 +996,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>46112</v>
       </c>
       <c r="B2" t="n">
@@ -931,7 +1015,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B3" t="n">
@@ -950,7 +1034,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>46114</v>
       </c>
       <c r="B4" t="n">
@@ -964,7 +1048,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>46115</v>
       </c>
       <c r="B5" t="n">
@@ -978,7 +1062,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>46116</v>
       </c>
       <c r="B6" t="n">
@@ -992,7 +1076,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>46117</v>
       </c>
       <c r="B7" t="n">
@@ -1006,7 +1090,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>46118</v>
       </c>
       <c r="B8" t="n">
@@ -1020,7 +1104,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>46119</v>
       </c>
       <c r="B9" t="n">
@@ -1034,7 +1118,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>46120</v>
       </c>
       <c r="B10" t="n">
@@ -1048,7 +1132,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>46121</v>
       </c>
       <c r="B11" t="n">
@@ -1062,7 +1146,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>46122</v>
       </c>
       <c r="B12" t="n">
@@ -1076,7 +1160,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>46123</v>
       </c>
       <c r="B13" t="n">
@@ -1090,7 +1174,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>46124</v>
       </c>
       <c r="B14" t="n">
@@ -1104,7 +1188,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>46125</v>
       </c>
       <c r="B15" t="n">
@@ -1118,7 +1202,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>46126</v>
       </c>
       <c r="B16" t="n">
@@ -1132,7 +1216,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>46127</v>
       </c>
       <c r="B17" t="n">
@@ -1146,7 +1230,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>46128</v>
       </c>
       <c r="B18" t="n">
@@ -1160,7 +1244,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>46129</v>
       </c>
       <c r="B19" t="n">
@@ -1174,7 +1258,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>46130</v>
       </c>
       <c r="B20" t="n">
@@ -1188,7 +1272,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>46131</v>
       </c>
       <c r="B21" t="n">
@@ -1202,7 +1286,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>46132</v>
       </c>
       <c r="B22" t="n">
@@ -1216,7 +1300,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>46133</v>
       </c>
       <c r="B23" t="n">
@@ -1230,7 +1314,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>46134</v>
       </c>
       <c r="B24" t="n">
@@ -1244,7 +1328,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>46135</v>
       </c>
       <c r="B25" t="n">
@@ -1258,7 +1342,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>46136</v>
       </c>
       <c r="B26" t="n">
@@ -1272,7 +1356,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>46137</v>
       </c>
       <c r="B27" t="n">
@@ -1283,7 +1367,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>46138</v>
       </c>
       <c r="B28" t="n">
@@ -1294,7 +1378,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>46139</v>
       </c>
       <c r="B29" t="n">
@@ -1305,7 +1389,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>46140</v>
       </c>
       <c r="B30" t="n">
@@ -1316,7 +1400,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>46141</v>
       </c>
       <c r="B31" t="n">
@@ -1330,7 +1414,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>46142</v>
       </c>
       <c r="B32" t="n">
@@ -1344,7 +1428,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B33" t="n">
@@ -1363,7 +1447,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>46144</v>
       </c>
       <c r="B34" t="n">
@@ -1377,7 +1461,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>46145</v>
       </c>
       <c r="B35" t="n">
@@ -1391,7 +1475,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>46146</v>
       </c>
       <c r="B36" t="n">
@@ -1405,7 +1489,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>46147</v>
       </c>
       <c r="B37" t="n">
@@ -1419,7 +1503,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>46148</v>
       </c>
       <c r="B38" t="n">
@@ -1433,7 +1517,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>46149</v>
       </c>
       <c r="B39" t="n">
@@ -1447,7 +1531,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>46150</v>
       </c>
       <c r="B40" t="n">
@@ -1461,7 +1545,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>46151</v>
       </c>
       <c r="B41" t="n">
@@ -1475,7 +1559,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>46152</v>
       </c>
       <c r="B42" t="n">
@@ -1489,7 +1573,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>46153</v>
       </c>
       <c r="B43" t="n">
@@ -1503,7 +1587,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>46154</v>
       </c>
       <c r="B44" t="n">
@@ -1517,7 +1601,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>46155</v>
       </c>
       <c r="B45" t="n">
@@ -1531,7 +1615,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>46156</v>
       </c>
       <c r="B46" t="n">
@@ -1545,7 +1629,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>46157</v>
       </c>
       <c r="B47" t="n">
@@ -1559,7 +1643,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>46158</v>
       </c>
       <c r="B48" t="n">
@@ -1573,7 +1657,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>46159</v>
       </c>
       <c r="B49" t="n">
@@ -1587,7 +1671,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>46160</v>
       </c>
       <c r="B50" t="n">
@@ -1601,7 +1685,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>46161</v>
       </c>
       <c r="B51" t="n">
@@ -1615,7 +1699,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>46162</v>
       </c>
       <c r="B52" t="n">
@@ -1629,7 +1713,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>46163</v>
       </c>
       <c r="B53" t="n">
@@ -1643,7 +1727,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>46164</v>
       </c>
       <c r="B54" t="n">
@@ -1657,7 +1741,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>46165</v>
       </c>
       <c r="B55" t="n">
@@ -1671,7 +1755,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>46166</v>
       </c>
       <c r="B56" t="n">
@@ -1682,7 +1766,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>46167</v>
       </c>
       <c r="B57" t="n">
@@ -1693,7 +1777,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>46168</v>
       </c>
       <c r="B58" t="n">
@@ -1704,7 +1788,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>46169</v>
       </c>
       <c r="B59" t="n">
@@ -1715,7 +1799,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>46170</v>
       </c>
       <c r="B60" t="n">
@@ -1726,7 +1810,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>46171</v>
       </c>
       <c r="B61" t="n">
@@ -1737,7 +1821,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46172</v>
       </c>
       <c r="B62" t="n">
@@ -1751,7 +1835,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46173</v>
       </c>
       <c r="B63" t="n">
@@ -1765,7 +1849,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B64" t="n">
@@ -1784,7 +1868,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46175</v>
       </c>
       <c r="B65" t="n">
@@ -1798,7 +1882,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46176</v>
       </c>
       <c r="B66" t="n">
@@ -1812,7 +1896,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46177</v>
       </c>
       <c r="B67" t="n">
@@ -1826,7 +1910,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46178</v>
       </c>
       <c r="B68" t="n">
@@ -1840,7 +1924,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>46179</v>
       </c>
       <c r="B69" t="n">
@@ -1854,7 +1938,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="n">
+      <c r="A70" s="3" t="n">
         <v>46180</v>
       </c>
       <c r="B70" t="n">
@@ -1868,7 +1952,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="n">
+      <c r="A71" s="3" t="n">
         <v>46181</v>
       </c>
       <c r="B71" t="n">
@@ -1882,7 +1966,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="n">
+      <c r="A72" s="3" t="n">
         <v>46182</v>
       </c>
       <c r="B72" t="n">
@@ -1896,7 +1980,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="n">
+      <c r="A73" s="3" t="n">
         <v>46183</v>
       </c>
       <c r="B73" t="n">
@@ -1910,7 +1994,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="n">
+      <c r="A74" s="3" t="n">
         <v>46184</v>
       </c>
       <c r="B74" t="n">
@@ -1924,7 +2008,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="n">
+      <c r="A75" s="3" t="n">
         <v>46185</v>
       </c>
       <c r="B75" t="n">
@@ -1938,7 +2022,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="n">
+      <c r="A76" s="3" t="n">
         <v>46186</v>
       </c>
       <c r="B76" t="n">
@@ -1952,7 +2036,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="n">
+      <c r="A77" s="3" t="n">
         <v>46187</v>
       </c>
       <c r="B77" t="n">
@@ -1966,7 +2050,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="n">
+      <c r="A78" s="3" t="n">
         <v>46188</v>
       </c>
       <c r="B78" t="n">
@@ -1980,7 +2064,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="n">
+      <c r="A79" s="3" t="n">
         <v>46189</v>
       </c>
       <c r="B79" t="n">
@@ -1994,7 +2078,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="n">
+      <c r="A80" s="3" t="n">
         <v>46190</v>
       </c>
       <c r="B80" t="n">
@@ -2008,7 +2092,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="n">
+      <c r="A81" s="3" t="n">
         <v>46191</v>
       </c>
       <c r="B81" t="n">
@@ -2022,7 +2106,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="n">
+      <c r="A82" s="3" t="n">
         <v>46192</v>
       </c>
       <c r="B82" t="n">
@@ -2036,7 +2120,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="n">
+      <c r="A83" s="3" t="n">
         <v>46193</v>
       </c>
       <c r="B83" t="n">
@@ -2050,7 +2134,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="n">
+      <c r="A84" s="3" t="n">
         <v>46194</v>
       </c>
       <c r="B84" t="n">
@@ -2064,7 +2148,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="n">
+      <c r="A85" s="3" t="n">
         <v>46195</v>
       </c>
       <c r="B85" t="n">
@@ -2078,7 +2162,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="n">
+      <c r="A86" s="3" t="n">
         <v>46196</v>
       </c>
       <c r="B86" t="n">
@@ -2092,7 +2176,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="n">
+      <c r="A87" s="3" t="n">
         <v>46197</v>
       </c>
       <c r="B87" t="n">
@@ -2106,7 +2190,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="n">
+      <c r="A88" s="3" t="n">
         <v>46198</v>
       </c>
       <c r="B88" t="n">
@@ -2120,7 +2204,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="n">
+      <c r="A89" s="3" t="n">
         <v>46199</v>
       </c>
       <c r="B89" t="n">
@@ -2134,7 +2218,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="n">
+      <c r="A90" s="3" t="n">
         <v>46200</v>
       </c>
       <c r="B90" t="n">
@@ -2145,7 +2229,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="n">
+      <c r="A91" s="3" t="n">
         <v>46201</v>
       </c>
       <c r="B91" t="n">
@@ -2156,7 +2240,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="n">
+      <c r="A92" s="3" t="n">
         <v>46202</v>
       </c>
       <c r="B92" t="n">
@@ -2167,7 +2251,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="n">
+      <c r="A93" s="3" t="n">
         <v>46203</v>
       </c>
       <c r="B93" t="n">
@@ -2181,7 +2265,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="n">
+      <c r="A94" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B94" t="n">
@@ -2200,7 +2284,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="n">
+      <c r="A95" s="3" t="n">
         <v>46205</v>
       </c>
       <c r="B95" t="n">
@@ -2214,7 +2298,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="n">
+      <c r="A96" s="3" t="n">
         <v>46206</v>
       </c>
       <c r="B96" t="n">
@@ -2228,7 +2312,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="n">
+      <c r="A97" s="3" t="n">
         <v>46207</v>
       </c>
       <c r="B97" t="n">
@@ -2242,7 +2326,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="n">
+      <c r="A98" s="3" t="n">
         <v>46208</v>
       </c>
       <c r="B98" t="n">
@@ -2256,7 +2340,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="n">
+      <c r="A99" s="3" t="n">
         <v>46209</v>
       </c>
       <c r="B99" t="n">
@@ -2270,7 +2354,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="n">
+      <c r="A100" s="3" t="n">
         <v>46210</v>
       </c>
       <c r="B100" t="n">
@@ -2284,7 +2368,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="n">
+      <c r="A101" s="3" t="n">
         <v>46211</v>
       </c>
       <c r="B101" t="n">
@@ -2298,7 +2382,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="n">
+      <c r="A102" s="3" t="n">
         <v>46212</v>
       </c>
       <c r="B102" t="n">
@@ -2312,7 +2396,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="n">
+      <c r="A103" s="3" t="n">
         <v>46213</v>
       </c>
       <c r="B103" t="n">
@@ -2326,7 +2410,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="n">
+      <c r="A104" s="3" t="n">
         <v>46214</v>
       </c>
       <c r="B104" t="n">
@@ -2340,7 +2424,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="n">
+      <c r="A105" s="3" t="n">
         <v>46215</v>
       </c>
       <c r="B105" t="n">
@@ -2354,7 +2438,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="n">
+      <c r="A106" s="3" t="n">
         <v>46216</v>
       </c>
       <c r="B106" t="n">
@@ -2368,7 +2452,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="n">
+      <c r="A107" s="3" t="n">
         <v>46217</v>
       </c>
       <c r="B107" t="n">
@@ -2382,7 +2466,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="n">
+      <c r="A108" s="3" t="n">
         <v>46218</v>
       </c>
       <c r="B108" t="n">
@@ -2396,7 +2480,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="n">
+      <c r="A109" s="3" t="n">
         <v>46219</v>
       </c>
       <c r="B109" t="n">
@@ -2410,7 +2494,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="n">
+      <c r="A110" s="3" t="n">
         <v>46220</v>
       </c>
       <c r="B110" t="n">
@@ -2424,7 +2508,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="n">
+      <c r="A111" s="3" t="n">
         <v>46221</v>
       </c>
       <c r="B111" t="n">
@@ -2438,7 +2522,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="n">
+      <c r="A112" s="3" t="n">
         <v>46222</v>
       </c>
       <c r="B112" t="n">
@@ -2452,7 +2536,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="n">
+      <c r="A113" s="3" t="n">
         <v>46223</v>
       </c>
       <c r="B113" t="n">
@@ -2466,7 +2550,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="n">
+      <c r="A114" s="3" t="n">
         <v>46224</v>
       </c>
       <c r="B114" t="n">
@@ -2480,7 +2564,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="n">
+      <c r="A115" s="3" t="n">
         <v>46225</v>
       </c>
       <c r="B115" t="n">
@@ -2494,7 +2578,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="n">
+      <c r="A116" s="3" t="n">
         <v>46226</v>
       </c>
       <c r="B116" t="n">
@@ -2508,7 +2592,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="n">
+      <c r="A117" s="3" t="n">
         <v>46227</v>
       </c>
       <c r="B117" t="n">
@@ -2522,7 +2606,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="n">
+      <c r="A118" s="3" t="n">
         <v>46228</v>
       </c>
       <c r="B118" t="n">
@@ -2536,7 +2620,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="n">
+      <c r="A119" s="3" t="n">
         <v>46229</v>
       </c>
       <c r="B119" t="n">
@@ -2547,7 +2631,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="n">
+      <c r="A120" s="3" t="n">
         <v>46230</v>
       </c>
       <c r="B120" t="n">
@@ -2558,7 +2642,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="n">
+      <c r="A121" s="3" t="n">
         <v>46231</v>
       </c>
       <c r="B121" t="n">
@@ -2569,7 +2653,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="n">
+      <c r="A122" s="3" t="n">
         <v>46232</v>
       </c>
       <c r="B122" t="n">
@@ -2580,7 +2664,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="n">
+      <c r="A123" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="B123" t="n">
@@ -2591,7 +2675,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="n">
+      <c r="A124" s="3" t="n">
         <v>46234</v>
       </c>
       <c r="B124" t="n">
@@ -2605,7 +2689,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="n">
+      <c r="A125" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B125" t="n">
@@ -2624,7 +2708,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="n">
+      <c r="A126" s="3" t="n">
         <v>46236</v>
       </c>
       <c r="B126" t="n">
@@ -2638,7 +2722,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="n">
+      <c r="A127" s="3" t="n">
         <v>46237</v>
       </c>
       <c r="B127" t="n">
@@ -2652,7 +2736,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="n">
+      <c r="A128" s="3" t="n">
         <v>46238</v>
       </c>
       <c r="B128" t="n">
@@ -2666,7 +2750,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="n">
+      <c r="A129" s="3" t="n">
         <v>46239</v>
       </c>
       <c r="B129" t="n">
@@ -2680,7 +2764,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="n">
+      <c r="A130" s="3" t="n">
         <v>46240</v>
       </c>
       <c r="B130" t="n">
@@ -2694,7 +2778,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="n">
+      <c r="A131" s="3" t="n">
         <v>46241</v>
       </c>
       <c r="B131" t="n">
@@ -2708,7 +2792,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="n">
+      <c r="A132" s="3" t="n">
         <v>46242</v>
       </c>
       <c r="B132" t="n">
@@ -2722,7 +2806,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="n">
+      <c r="A133" s="3" t="n">
         <v>46243</v>
       </c>
       <c r="B133" t="n">
@@ -2736,7 +2820,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="n">
+      <c r="A134" s="3" t="n">
         <v>46244</v>
       </c>
       <c r="B134" t="n">
@@ -2750,7 +2834,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="n">
+      <c r="A135" s="3" t="n">
         <v>46245</v>
       </c>
       <c r="B135" t="n">
@@ -2764,7 +2848,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="n">
+      <c r="A136" s="3" t="n">
         <v>46246</v>
       </c>
       <c r="B136" t="n">
@@ -2778,7 +2862,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="n">
+      <c r="A137" s="3" t="n">
         <v>46247</v>
       </c>
       <c r="B137" t="n">
@@ -2792,7 +2876,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="n">
+      <c r="A138" s="3" t="n">
         <v>46248</v>
       </c>
       <c r="B138" t="n">
@@ -2806,7 +2890,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="n">
+      <c r="A139" s="3" t="n">
         <v>46249</v>
       </c>
       <c r="B139" t="n">
@@ -2820,7 +2904,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="n">
+      <c r="A140" s="3" t="n">
         <v>46250</v>
       </c>
       <c r="B140" t="n">
@@ -2834,7 +2918,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="5" t="n">
+      <c r="A141" s="3" t="n">
         <v>46251</v>
       </c>
       <c r="B141" t="n">
@@ -2848,7 +2932,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="5" t="n">
+      <c r="A142" s="3" t="n">
         <v>46252</v>
       </c>
       <c r="B142" t="n">
@@ -2862,7 +2946,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="n">
+      <c r="A143" s="3" t="n">
         <v>46253</v>
       </c>
       <c r="B143" t="n">
@@ -2876,7 +2960,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="5" t="n">
+      <c r="A144" s="3" t="n">
         <v>46254</v>
       </c>
       <c r="B144" t="n">
@@ -2890,7 +2974,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="n">
+      <c r="A145" s="3" t="n">
         <v>46255</v>
       </c>
       <c r="B145" t="n">
@@ -2904,7 +2988,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="5" t="n">
+      <c r="A146" s="3" t="n">
         <v>46256</v>
       </c>
       <c r="B146" t="n">
@@ -2918,7 +3002,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="5" t="n">
+      <c r="A147" s="3" t="n">
         <v>46257</v>
       </c>
       <c r="B147" t="n">
@@ -2932,7 +3016,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="5" t="n">
+      <c r="A148" s="3" t="n">
         <v>46258</v>
       </c>
       <c r="B148" t="n">
@@ -2946,7 +3030,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="5" t="n">
+      <c r="A149" s="3" t="n">
         <v>46259</v>
       </c>
       <c r="B149" t="n">
@@ -2960,7 +3044,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="n">
+      <c r="A150" s="3" t="n">
         <v>46260</v>
       </c>
       <c r="B150" t="n">
@@ -2974,7 +3058,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="5" t="n">
+      <c r="A151" s="3" t="n">
         <v>46261</v>
       </c>
       <c r="B151" t="n">
@@ -2988,7 +3072,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="5" t="n">
+      <c r="A152" s="3" t="n">
         <v>46262</v>
       </c>
       <c r="B152" t="n">
@@ -3002,7 +3086,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="5" t="n">
+      <c r="A153" s="3" t="n">
         <v>46263</v>
       </c>
       <c r="B153" t="n">
@@ -3016,7 +3100,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="n">
+      <c r="A154" s="3" t="n">
         <v>46264</v>
       </c>
       <c r="B154" t="n">
@@ -3030,7 +3114,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="5" t="n">
+      <c r="A155" s="3" t="n">
         <v>46265</v>
       </c>
       <c r="B155" t="n">
@@ -3044,7 +3128,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="5" t="n">
+      <c r="A156" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B156" t="n">
@@ -3063,7 +3147,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="5" t="n">
+      <c r="A157" s="3" t="n">
         <v>46267</v>
       </c>
       <c r="B157" t="n">
@@ -3077,7 +3161,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="5" t="n">
+      <c r="A158" s="3" t="n">
         <v>46268</v>
       </c>
       <c r="B158" t="n">
@@ -3091,7 +3175,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="5" t="n">
+      <c r="A159" s="3" t="n">
         <v>46269</v>
       </c>
       <c r="B159" t="n">
@@ -3105,7 +3189,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="5" t="n">
+      <c r="A160" s="3" t="n">
         <v>46270</v>
       </c>
       <c r="B160" t="n">
@@ -3119,7 +3203,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="5" t="n">
+      <c r="A161" s="3" t="n">
         <v>46271</v>
       </c>
       <c r="B161" t="n">
@@ -3133,7 +3217,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="5" t="n">
+      <c r="A162" s="3" t="n">
         <v>46272</v>
       </c>
       <c r="B162" t="n">
@@ -3147,7 +3231,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="5" t="n">
+      <c r="A163" s="3" t="n">
         <v>46273</v>
       </c>
       <c r="B163" t="n">
@@ -3158,7 +3242,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="5" t="n">
+      <c r="A164" s="3" t="n">
         <v>46274</v>
       </c>
       <c r="B164" t="n">
@@ -3169,7 +3253,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="5" t="n">
+      <c r="A165" s="3" t="n">
         <v>46275</v>
       </c>
       <c r="B165" t="n">
@@ -3180,7 +3264,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="5" t="n">
+      <c r="A166" s="3" t="n">
         <v>46276</v>
       </c>
       <c r="B166" t="n">
@@ -3191,7 +3275,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="5" t="n">
+      <c r="A167" s="3" t="n">
         <v>46277</v>
       </c>
       <c r="B167" t="n">
@@ -3202,7 +3286,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="5" t="n">
+      <c r="A168" s="3" t="n">
         <v>46278</v>
       </c>
       <c r="B168" t="n">
@@ -3213,7 +3297,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="5" t="n">
+      <c r="A169" s="3" t="n">
         <v>46279</v>
       </c>
       <c r="B169" t="n">
@@ -3227,7 +3311,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="5" t="n">
+      <c r="A170" s="3" t="n">
         <v>46280</v>
       </c>
       <c r="B170" t="n">
@@ -3241,7 +3325,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="5" t="n">
+      <c r="A171" s="3" t="n">
         <v>46281</v>
       </c>
       <c r="B171" t="n">
@@ -3255,7 +3339,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="5" t="n">
+      <c r="A172" s="3" t="n">
         <v>46282</v>
       </c>
       <c r="B172" t="n">
@@ -3269,7 +3353,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="5" t="n">
+      <c r="A173" s="3" t="n">
         <v>46283</v>
       </c>
       <c r="B173" t="n">
@@ -3283,7 +3367,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="5" t="n">
+      <c r="A174" s="3" t="n">
         <v>46284</v>
       </c>
       <c r="B174" t="n">
@@ -3297,7 +3381,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="5" t="n">
+      <c r="A175" s="3" t="n">
         <v>46285</v>
       </c>
       <c r="B175" t="n">
@@ -3311,7 +3395,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="5" t="n">
+      <c r="A176" s="3" t="n">
         <v>46286</v>
       </c>
       <c r="B176" t="n">
@@ -3325,7 +3409,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="5" t="n">
+      <c r="A177" s="3" t="n">
         <v>46287</v>
       </c>
       <c r="B177" t="n">
@@ -3339,7 +3423,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="5" t="n">
+      <c r="A178" s="3" t="n">
         <v>46288</v>
       </c>
       <c r="B178" t="n">
@@ -3353,7 +3437,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="5" t="n">
+      <c r="A179" s="3" t="n">
         <v>46289</v>
       </c>
       <c r="B179" t="n">
@@ -3367,7 +3451,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="5" t="n">
+      <c r="A180" s="3" t="n">
         <v>46290</v>
       </c>
       <c r="B180" t="n">
@@ -3381,7 +3465,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="5" t="n">
+      <c r="A181" s="3" t="n">
         <v>46291</v>
       </c>
       <c r="B181" t="n">
@@ -3395,7 +3479,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="5" t="n">
+      <c r="A182" s="3" t="n">
         <v>46292</v>
       </c>
       <c r="B182" t="n">
@@ -3409,7 +3493,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="5" t="n">
+      <c r="A183" s="3" t="n">
         <v>46293</v>
       </c>
       <c r="B183" t="n">
@@ -3419,7 +3503,54 @@
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>174.542222</v>
+        <v>174.5</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B184" t="n">
+        <v>16.846274</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" t="n">
+        <v>145.544444</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B185" t="n">
+        <v>22.682036</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0</v>
+      </c>
+      <c r="D185" t="n">
+        <v>136.055556</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B186" t="n">
+        <v>22.166621</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0</v>
+      </c>
+      <c r="D186" t="n">
+        <v>141.777778</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Oct/26</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3434,7 +3565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E183"/>
+  <dimension ref="A1:E186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3468,7 +3599,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>46112</v>
       </c>
       <c r="B2" t="n">
@@ -3487,7 +3618,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B3" t="n">
@@ -3506,7 +3637,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>46114</v>
       </c>
       <c r="B4" t="n">
@@ -3520,7 +3651,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>46115</v>
       </c>
       <c r="B5" t="n">
@@ -3534,7 +3665,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>46116</v>
       </c>
       <c r="B6" t="n">
@@ -3548,7 +3679,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>46117</v>
       </c>
       <c r="B7" t="n">
@@ -3562,7 +3693,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>46118</v>
       </c>
       <c r="B8" t="n">
@@ -3576,7 +3707,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>46119</v>
       </c>
       <c r="B9" t="n">
@@ -3590,7 +3721,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>46120</v>
       </c>
       <c r="B10" t="n">
@@ -3604,7 +3735,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>46121</v>
       </c>
       <c r="B11" t="n">
@@ -3618,7 +3749,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>46122</v>
       </c>
       <c r="B12" t="n">
@@ -3632,7 +3763,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>46123</v>
       </c>
       <c r="B13" t="n">
@@ -3646,7 +3777,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>46124</v>
       </c>
       <c r="B14" t="n">
@@ -3660,7 +3791,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>46125</v>
       </c>
       <c r="B15" t="n">
@@ -3674,7 +3805,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>46126</v>
       </c>
       <c r="B16" t="n">
@@ -3688,7 +3819,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>46127</v>
       </c>
       <c r="B17" t="n">
@@ -3702,7 +3833,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>46128</v>
       </c>
       <c r="B18" t="n">
@@ -3716,7 +3847,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>46129</v>
       </c>
       <c r="B19" t="n">
@@ -3730,7 +3861,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>46130</v>
       </c>
       <c r="B20" t="n">
@@ -3744,7 +3875,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>46131</v>
       </c>
       <c r="B21" t="n">
@@ -3758,7 +3889,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>46132</v>
       </c>
       <c r="B22" t="n">
@@ -3772,7 +3903,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>46133</v>
       </c>
       <c r="B23" t="n">
@@ -3786,7 +3917,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>46134</v>
       </c>
       <c r="B24" t="n">
@@ -3800,7 +3931,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>46135</v>
       </c>
       <c r="B25" t="n">
@@ -3814,7 +3945,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>46136</v>
       </c>
       <c r="B26" t="n">
@@ -3828,7 +3959,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>46137</v>
       </c>
       <c r="B27" t="n">
@@ -3842,7 +3973,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>46138</v>
       </c>
       <c r="B28" t="n">
@@ -3856,7 +3987,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>46139</v>
       </c>
       <c r="B29" t="n">
@@ -3870,7 +4001,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>46140</v>
       </c>
       <c r="B30" t="n">
@@ -3884,7 +4015,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>46141</v>
       </c>
       <c r="B31" t="n">
@@ -3898,7 +4029,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>46142</v>
       </c>
       <c r="B32" t="n">
@@ -3912,7 +4043,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B33" t="n">
@@ -3931,7 +4062,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>46144</v>
       </c>
       <c r="B34" t="n">
@@ -3945,7 +4076,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>46145</v>
       </c>
       <c r="B35" t="n">
@@ -3959,7 +4090,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>46146</v>
       </c>
       <c r="B36" t="n">
@@ -3973,7 +4104,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>46147</v>
       </c>
       <c r="B37" t="n">
@@ -3987,7 +4118,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>46148</v>
       </c>
       <c r="B38" t="n">
@@ -4001,7 +4132,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>46149</v>
       </c>
       <c r="B39" t="n">
@@ -4015,7 +4146,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>46150</v>
       </c>
       <c r="B40" t="n">
@@ -4029,7 +4160,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>46151</v>
       </c>
       <c r="B41" t="n">
@@ -4043,7 +4174,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>46152</v>
       </c>
       <c r="B42" t="n">
@@ -4057,7 +4188,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>46153</v>
       </c>
       <c r="B43" t="n">
@@ -4071,7 +4202,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>46154</v>
       </c>
       <c r="B44" t="n">
@@ -4085,7 +4216,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>46155</v>
       </c>
       <c r="B45" t="n">
@@ -4099,7 +4230,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>46156</v>
       </c>
       <c r="B46" t="n">
@@ -4113,7 +4244,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>46157</v>
       </c>
       <c r="B47" t="n">
@@ -4127,7 +4258,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>46158</v>
       </c>
       <c r="B48" t="n">
@@ -4141,7 +4272,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>46159</v>
       </c>
       <c r="B49" t="n">
@@ -4155,7 +4286,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>46160</v>
       </c>
       <c r="B50" t="n">
@@ -4169,7 +4300,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>46161</v>
       </c>
       <c r="B51" t="n">
@@ -4183,7 +4314,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>46162</v>
       </c>
       <c r="B52" t="n">
@@ -4197,7 +4328,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>46163</v>
       </c>
       <c r="B53" t="n">
@@ -4211,7 +4342,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>46164</v>
       </c>
       <c r="B54" t="n">
@@ -4225,7 +4356,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>46165</v>
       </c>
       <c r="B55" t="n">
@@ -4239,7 +4370,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>46166</v>
       </c>
       <c r="B56" t="n">
@@ -4253,7 +4384,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>46167</v>
       </c>
       <c r="B57" t="n">
@@ -4267,7 +4398,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>46168</v>
       </c>
       <c r="B58" t="n">
@@ -4281,7 +4412,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>46169</v>
       </c>
       <c r="B59" t="n">
@@ -4295,7 +4426,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>46170</v>
       </c>
       <c r="B60" t="n">
@@ -4309,7 +4440,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>46171</v>
       </c>
       <c r="B61" t="n">
@@ -4323,7 +4454,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46172</v>
       </c>
       <c r="B62" t="n">
@@ -4337,7 +4468,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46173</v>
       </c>
       <c r="B63" t="n">
@@ -4351,7 +4482,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B64" t="n">
@@ -4370,7 +4501,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>46175</v>
       </c>
       <c r="B65" t="n">
@@ -4384,7 +4515,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>46176</v>
       </c>
       <c r="B66" t="n">
@@ -4398,7 +4529,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>46177</v>
       </c>
       <c r="B67" t="n">
@@ -4412,7 +4543,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>46178</v>
       </c>
       <c r="B68" t="n">
@@ -4426,7 +4557,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>46179</v>
       </c>
       <c r="B69" t="n">
@@ -4440,7 +4571,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="n">
+      <c r="A70" s="3" t="n">
         <v>46180</v>
       </c>
       <c r="B70" t="n">
@@ -4454,7 +4585,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="n">
+      <c r="A71" s="3" t="n">
         <v>46181</v>
       </c>
       <c r="B71" t="n">
@@ -4468,7 +4599,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="n">
+      <c r="A72" s="3" t="n">
         <v>46182</v>
       </c>
       <c r="B72" t="n">
@@ -4482,7 +4613,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="n">
+      <c r="A73" s="3" t="n">
         <v>46183</v>
       </c>
       <c r="B73" t="n">
@@ -4496,7 +4627,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="n">
+      <c r="A74" s="3" t="n">
         <v>46184</v>
       </c>
       <c r="B74" t="n">
@@ -4510,7 +4641,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="n">
+      <c r="A75" s="3" t="n">
         <v>46185</v>
       </c>
       <c r="B75" t="n">
@@ -4524,7 +4655,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="n">
+      <c r="A76" s="3" t="n">
         <v>46186</v>
       </c>
       <c r="B76" t="n">
@@ -4538,7 +4669,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="n">
+      <c r="A77" s="3" t="n">
         <v>46187</v>
       </c>
       <c r="B77" t="n">
@@ -4552,7 +4683,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="n">
+      <c r="A78" s="3" t="n">
         <v>46188</v>
       </c>
       <c r="B78" t="n">
@@ -4566,7 +4697,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="n">
+      <c r="A79" s="3" t="n">
         <v>46189</v>
       </c>
       <c r="B79" t="n">
@@ -4580,7 +4711,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="n">
+      <c r="A80" s="3" t="n">
         <v>46190</v>
       </c>
       <c r="B80" t="n">
@@ -4594,7 +4725,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="n">
+      <c r="A81" s="3" t="n">
         <v>46191</v>
       </c>
       <c r="B81" t="n">
@@ -4608,7 +4739,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="n">
+      <c r="A82" s="3" t="n">
         <v>46192</v>
       </c>
       <c r="B82" t="n">
@@ -4622,7 +4753,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="n">
+      <c r="A83" s="3" t="n">
         <v>46193</v>
       </c>
       <c r="B83" t="n">
@@ -4636,7 +4767,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="n">
+      <c r="A84" s="3" t="n">
         <v>46194</v>
       </c>
       <c r="B84" t="n">
@@ -4650,7 +4781,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="n">
+      <c r="A85" s="3" t="n">
         <v>46195</v>
       </c>
       <c r="B85" t="n">
@@ -4664,7 +4795,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="n">
+      <c r="A86" s="3" t="n">
         <v>46196</v>
       </c>
       <c r="B86" t="n">
@@ -4678,7 +4809,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="n">
+      <c r="A87" s="3" t="n">
         <v>46197</v>
       </c>
       <c r="B87" t="n">
@@ -4692,7 +4823,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="n">
+      <c r="A88" s="3" t="n">
         <v>46198</v>
       </c>
       <c r="B88" t="n">
@@ -4706,7 +4837,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="n">
+      <c r="A89" s="3" t="n">
         <v>46199</v>
       </c>
       <c r="B89" t="n">
@@ -4720,7 +4851,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="n">
+      <c r="A90" s="3" t="n">
         <v>46200</v>
       </c>
       <c r="B90" t="n">
@@ -4734,7 +4865,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="n">
+      <c r="A91" s="3" t="n">
         <v>46201</v>
       </c>
       <c r="B91" t="n">
@@ -4748,7 +4879,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="n">
+      <c r="A92" s="3" t="n">
         <v>46202</v>
       </c>
       <c r="B92" t="n">
@@ -4762,7 +4893,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="n">
+      <c r="A93" s="3" t="n">
         <v>46203</v>
       </c>
       <c r="B93" t="n">
@@ -4776,7 +4907,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="n">
+      <c r="A94" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B94" t="n">
@@ -4795,7 +4926,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="n">
+      <c r="A95" s="3" t="n">
         <v>46205</v>
       </c>
       <c r="B95" t="n">
@@ -4809,7 +4940,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="n">
+      <c r="A96" s="3" t="n">
         <v>46206</v>
       </c>
       <c r="B96" t="n">
@@ -4823,7 +4954,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="n">
+      <c r="A97" s="3" t="n">
         <v>46207</v>
       </c>
       <c r="B97" t="n">
@@ -4837,7 +4968,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="n">
+      <c r="A98" s="3" t="n">
         <v>46208</v>
       </c>
       <c r="B98" t="n">
@@ -4851,7 +4982,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="n">
+      <c r="A99" s="3" t="n">
         <v>46209</v>
       </c>
       <c r="B99" t="n">
@@ -4865,7 +4996,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="n">
+      <c r="A100" s="3" t="n">
         <v>46210</v>
       </c>
       <c r="B100" t="n">
@@ -4879,7 +5010,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="n">
+      <c r="A101" s="3" t="n">
         <v>46211</v>
       </c>
       <c r="B101" t="n">
@@ -4893,7 +5024,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="n">
+      <c r="A102" s="3" t="n">
         <v>46212</v>
       </c>
       <c r="B102" t="n">
@@ -4907,7 +5038,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="n">
+      <c r="A103" s="3" t="n">
         <v>46213</v>
       </c>
       <c r="B103" t="n">
@@ -4921,7 +5052,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="n">
+      <c r="A104" s="3" t="n">
         <v>46214</v>
       </c>
       <c r="B104" t="n">
@@ -4935,7 +5066,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="n">
+      <c r="A105" s="3" t="n">
         <v>46215</v>
       </c>
       <c r="B105" t="n">
@@ -4949,7 +5080,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="n">
+      <c r="A106" s="3" t="n">
         <v>46216</v>
       </c>
       <c r="B106" t="n">
@@ -4963,7 +5094,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="n">
+      <c r="A107" s="3" t="n">
         <v>46217</v>
       </c>
       <c r="B107" t="n">
@@ -4977,7 +5108,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="n">
+      <c r="A108" s="3" t="n">
         <v>46218</v>
       </c>
       <c r="B108" t="n">
@@ -4991,7 +5122,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="n">
+      <c r="A109" s="3" t="n">
         <v>46219</v>
       </c>
       <c r="B109" t="n">
@@ -5005,7 +5136,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="n">
+      <c r="A110" s="3" t="n">
         <v>46220</v>
       </c>
       <c r="B110" t="n">
@@ -5019,7 +5150,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="n">
+      <c r="A111" s="3" t="n">
         <v>46221</v>
       </c>
       <c r="B111" t="n">
@@ -5033,7 +5164,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="n">
+      <c r="A112" s="3" t="n">
         <v>46222</v>
       </c>
       <c r="B112" t="n">
@@ -5047,7 +5178,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="n">
+      <c r="A113" s="3" t="n">
         <v>46223</v>
       </c>
       <c r="B113" t="n">
@@ -5061,7 +5192,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="n">
+      <c r="A114" s="3" t="n">
         <v>46224</v>
       </c>
       <c r="B114" t="n">
@@ -5075,7 +5206,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="n">
+      <c r="A115" s="3" t="n">
         <v>46225</v>
       </c>
       <c r="B115" t="n">
@@ -5089,7 +5220,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="n">
+      <c r="A116" s="3" t="n">
         <v>46226</v>
       </c>
       <c r="B116" t="n">
@@ -5103,7 +5234,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="n">
+      <c r="A117" s="3" t="n">
         <v>46227</v>
       </c>
       <c r="B117" t="n">
@@ -5117,7 +5248,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="n">
+      <c r="A118" s="3" t="n">
         <v>46228</v>
       </c>
       <c r="B118" t="n">
@@ -5131,7 +5262,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="n">
+      <c r="A119" s="3" t="n">
         <v>46229</v>
       </c>
       <c r="B119" t="n">
@@ -5145,7 +5276,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="n">
+      <c r="A120" s="3" t="n">
         <v>46230</v>
       </c>
       <c r="B120" t="n">
@@ -5159,7 +5290,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="n">
+      <c r="A121" s="3" t="n">
         <v>46231</v>
       </c>
       <c r="B121" t="n">
@@ -5173,7 +5304,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="n">
+      <c r="A122" s="3" t="n">
         <v>46232</v>
       </c>
       <c r="B122" t="n">
@@ -5187,7 +5318,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="n">
+      <c r="A123" s="3" t="n">
         <v>46233</v>
       </c>
       <c r="B123" t="n">
@@ -5201,7 +5332,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="n">
+      <c r="A124" s="3" t="n">
         <v>46234</v>
       </c>
       <c r="B124" t="n">
@@ -5215,7 +5346,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="n">
+      <c r="A125" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B125" t="n">
@@ -5234,7 +5365,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="n">
+      <c r="A126" s="3" t="n">
         <v>46236</v>
       </c>
       <c r="B126" t="n">
@@ -5248,7 +5379,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="n">
+      <c r="A127" s="3" t="n">
         <v>46237</v>
       </c>
       <c r="B127" t="n">
@@ -5262,7 +5393,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="n">
+      <c r="A128" s="3" t="n">
         <v>46238</v>
       </c>
       <c r="B128" t="n">
@@ -5276,7 +5407,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="n">
+      <c r="A129" s="3" t="n">
         <v>46239</v>
       </c>
       <c r="B129" t="n">
@@ -5290,7 +5421,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="n">
+      <c r="A130" s="3" t="n">
         <v>46240</v>
       </c>
       <c r="B130" t="n">
@@ -5304,7 +5435,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="n">
+      <c r="A131" s="3" t="n">
         <v>46241</v>
       </c>
       <c r="B131" t="n">
@@ -5318,7 +5449,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="n">
+      <c r="A132" s="3" t="n">
         <v>46242</v>
       </c>
       <c r="B132" t="n">
@@ -5332,7 +5463,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="n">
+      <c r="A133" s="3" t="n">
         <v>46243</v>
       </c>
       <c r="B133" t="n">
@@ -5346,7 +5477,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="n">
+      <c r="A134" s="3" t="n">
         <v>46244</v>
       </c>
       <c r="B134" t="n">
@@ -5360,7 +5491,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="n">
+      <c r="A135" s="3" t="n">
         <v>46245</v>
       </c>
       <c r="B135" t="n">
@@ -5374,7 +5505,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="n">
+      <c r="A136" s="3" t="n">
         <v>46246</v>
       </c>
       <c r="B136" t="n">
@@ -5388,7 +5519,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="n">
+      <c r="A137" s="3" t="n">
         <v>46247</v>
       </c>
       <c r="B137" t="n">
@@ -5402,7 +5533,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="n">
+      <c r="A138" s="3" t="n">
         <v>46248</v>
       </c>
       <c r="B138" t="n">
@@ -5416,7 +5547,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="n">
+      <c r="A139" s="3" t="n">
         <v>46249</v>
       </c>
       <c r="B139" t="n">
@@ -5430,7 +5561,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="n">
+      <c r="A140" s="3" t="n">
         <v>46250</v>
       </c>
       <c r="B140" t="n">
@@ -5444,7 +5575,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="5" t="n">
+      <c r="A141" s="3" t="n">
         <v>46251</v>
       </c>
       <c r="B141" t="n">
@@ -5458,7 +5589,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="5" t="n">
+      <c r="A142" s="3" t="n">
         <v>46252</v>
       </c>
       <c r="B142" t="n">
@@ -5472,7 +5603,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="n">
+      <c r="A143" s="3" t="n">
         <v>46253</v>
       </c>
       <c r="B143" t="n">
@@ -5486,7 +5617,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="5" t="n">
+      <c r="A144" s="3" t="n">
         <v>46254</v>
       </c>
       <c r="B144" t="n">
@@ -5500,7 +5631,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="n">
+      <c r="A145" s="3" t="n">
         <v>46255</v>
       </c>
       <c r="B145" t="n">
@@ -5514,7 +5645,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="5" t="n">
+      <c r="A146" s="3" t="n">
         <v>46256</v>
       </c>
       <c r="B146" t="n">
@@ -5528,7 +5659,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="5" t="n">
+      <c r="A147" s="3" t="n">
         <v>46257</v>
       </c>
       <c r="B147" t="n">
@@ -5542,7 +5673,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="5" t="n">
+      <c r="A148" s="3" t="n">
         <v>46258</v>
       </c>
       <c r="B148" t="n">
@@ -5556,7 +5687,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="5" t="n">
+      <c r="A149" s="3" t="n">
         <v>46259</v>
       </c>
       <c r="B149" t="n">
@@ -5570,7 +5701,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="n">
+      <c r="A150" s="3" t="n">
         <v>46260</v>
       </c>
       <c r="B150" t="n">
@@ -5584,7 +5715,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="5" t="n">
+      <c r="A151" s="3" t="n">
         <v>46261</v>
       </c>
       <c r="B151" t="n">
@@ -5598,7 +5729,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="5" t="n">
+      <c r="A152" s="3" t="n">
         <v>46262</v>
       </c>
       <c r="B152" t="n">
@@ -5612,7 +5743,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="5" t="n">
+      <c r="A153" s="3" t="n">
         <v>46263</v>
       </c>
       <c r="B153" t="n">
@@ -5626,7 +5757,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="n">
+      <c r="A154" s="3" t="n">
         <v>46264</v>
       </c>
       <c r="B154" t="n">
@@ -5640,7 +5771,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="5" t="n">
+      <c r="A155" s="3" t="n">
         <v>46265</v>
       </c>
       <c r="B155" t="n">
@@ -5654,7 +5785,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="5" t="n">
+      <c r="A156" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B156" t="n">
@@ -5673,7 +5804,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="5" t="n">
+      <c r="A157" s="3" t="n">
         <v>46267</v>
       </c>
       <c r="B157" t="n">
@@ -5687,7 +5818,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="5" t="n">
+      <c r="A158" s="3" t="n">
         <v>46268</v>
       </c>
       <c r="B158" t="n">
@@ -5701,7 +5832,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="5" t="n">
+      <c r="A159" s="3" t="n">
         <v>46269</v>
       </c>
       <c r="B159" t="n">
@@ -5715,7 +5846,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="5" t="n">
+      <c r="A160" s="3" t="n">
         <v>46270</v>
       </c>
       <c r="B160" t="n">
@@ -5729,7 +5860,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="5" t="n">
+      <c r="A161" s="3" t="n">
         <v>46271</v>
       </c>
       <c r="B161" t="n">
@@ -5743,7 +5874,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="5" t="n">
+      <c r="A162" s="3" t="n">
         <v>46272</v>
       </c>
       <c r="B162" t="n">
@@ -5757,7 +5888,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="5" t="n">
+      <c r="A163" s="3" t="n">
         <v>46273</v>
       </c>
       <c r="B163" t="n">
@@ -5771,7 +5902,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="5" t="n">
+      <c r="A164" s="3" t="n">
         <v>46274</v>
       </c>
       <c r="B164" t="n">
@@ -5785,7 +5916,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="5" t="n">
+      <c r="A165" s="3" t="n">
         <v>46275</v>
       </c>
       <c r="B165" t="n">
@@ -5799,7 +5930,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="5" t="n">
+      <c r="A166" s="3" t="n">
         <v>46276</v>
       </c>
       <c r="B166" t="n">
@@ -5813,7 +5944,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="5" t="n">
+      <c r="A167" s="3" t="n">
         <v>46277</v>
       </c>
       <c r="B167" t="n">
@@ -5827,7 +5958,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="5" t="n">
+      <c r="A168" s="3" t="n">
         <v>46278</v>
       </c>
       <c r="B168" t="n">
@@ -5841,7 +5972,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="5" t="n">
+      <c r="A169" s="3" t="n">
         <v>46279</v>
       </c>
       <c r="B169" t="n">
@@ -5855,7 +5986,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="5" t="n">
+      <c r="A170" s="3" t="n">
         <v>46280</v>
       </c>
       <c r="B170" t="n">
@@ -5869,7 +6000,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="5" t="n">
+      <c r="A171" s="3" t="n">
         <v>46281</v>
       </c>
       <c r="B171" t="n">
@@ -5883,7 +6014,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="5" t="n">
+      <c r="A172" s="3" t="n">
         <v>46282</v>
       </c>
       <c r="B172" t="n">
@@ -5897,7 +6028,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="5" t="n">
+      <c r="A173" s="3" t="n">
         <v>46283</v>
       </c>
       <c r="B173" t="n">
@@ -5911,7 +6042,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="5" t="n">
+      <c r="A174" s="3" t="n">
         <v>46284</v>
       </c>
       <c r="B174" t="n">
@@ -5925,7 +6056,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="5" t="n">
+      <c r="A175" s="3" t="n">
         <v>46285</v>
       </c>
       <c r="B175" t="n">
@@ -5939,7 +6070,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="5" t="n">
+      <c r="A176" s="3" t="n">
         <v>46286</v>
       </c>
       <c r="B176" t="n">
@@ -5953,7 +6084,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="5" t="n">
+      <c r="A177" s="3" t="n">
         <v>46287</v>
       </c>
       <c r="B177" t="n">
@@ -5967,7 +6098,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="5" t="n">
+      <c r="A178" s="3" t="n">
         <v>46288</v>
       </c>
       <c r="B178" t="n">
@@ -5981,7 +6112,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="5" t="n">
+      <c r="A179" s="3" t="n">
         <v>46289</v>
       </c>
       <c r="B179" t="n">
@@ -5995,7 +6126,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="5" t="n">
+      <c r="A180" s="3" t="n">
         <v>46290</v>
       </c>
       <c r="B180" t="n">
@@ -6009,7 +6140,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="5" t="n">
+      <c r="A181" s="3" t="n">
         <v>46291</v>
       </c>
       <c r="B181" t="n">
@@ -6023,7 +6154,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="5" t="n">
+      <c r="A182" s="3" t="n">
         <v>46292</v>
       </c>
       <c r="B182" t="n">
@@ -6037,17 +6168,64 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="5" t="n">
+      <c r="A183" s="3" t="n">
         <v>46293</v>
       </c>
       <c r="B183" t="n">
         <v>97.82638999999999</v>
       </c>
       <c r="C183" t="n">
-        <v>8.150091</v>
+        <v>8.316767</v>
       </c>
       <c r="D183" t="n">
-        <v>14.348428</v>
+        <v>14.181752</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B184" t="n">
+        <v>81.78750099999999</v>
+      </c>
+      <c r="C184" t="n">
+        <v>8.429243999999999</v>
+      </c>
+      <c r="D184" t="n">
+        <v>15.025879</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B185" t="n">
+        <v>81.70446099999999</v>
+      </c>
+      <c r="C185" t="n">
+        <v>8.294691</v>
+      </c>
+      <c r="D185" t="n">
+        <v>13.900176</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B186" t="n">
+        <v>83.032483</v>
+      </c>
+      <c r="C186" t="n">
+        <v>8.350685</v>
+      </c>
+      <c r="D186" t="n">
+        <v>14.789819</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Oct/26</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6062,7 +6240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E183"/>
+  <dimension ref="A1:E186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9102,7 +9280,7 @@
         <v>46293</v>
       </c>
       <c r="B183" t="n">
-        <v>197.026459</v>
+        <v>196.984237</v>
       </c>
       <c r="C183" t="n">
         <v>22.240846</v>
@@ -9111,7 +9289,58 @@
         <v>0</v>
       </c>
       <c r="E183" t="n">
-        <v>174.542222</v>
+        <v>174.5</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B184" t="n">
+        <v>162.565227</v>
+      </c>
+      <c r="C184" t="n">
+        <v>16.846274</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="n">
+        <v>145.544444</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B185" t="n">
+        <v>158.857138</v>
+      </c>
+      <c r="C185" t="n">
+        <v>22.682036</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" t="n">
+        <v>136.055556</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B186" t="n">
+        <v>164.07468</v>
+      </c>
+      <c r="C186" t="n">
+        <v>22.166621</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" t="n">
+        <v>141.777778</v>
       </c>
     </row>
   </sheetData>
@@ -9125,7 +9354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:F186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12785,10 +13014,10 @@
         <v>46293</v>
       </c>
       <c r="B183" t="n">
-        <v>8.150091</v>
+        <v>8.316767</v>
       </c>
       <c r="C183" t="n">
-        <v>14.348428</v>
+        <v>14.181752</v>
       </c>
       <c r="D183" t="n">
         <v>113.16603</v>
@@ -12798,6 +13027,66 @@
       </c>
       <c r="F183" t="n">
         <v>156.435753</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B184" t="n">
+        <v>8.429243999999999</v>
+      </c>
+      <c r="C184" t="n">
+        <v>15.025879</v>
+      </c>
+      <c r="D184" t="n">
+        <v>96.78906599999999</v>
+      </c>
+      <c r="E184" t="n">
+        <v>81.78750099999999</v>
+      </c>
+      <c r="F184" t="n">
+        <v>136.173511</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B185" t="n">
+        <v>8.294691</v>
+      </c>
+      <c r="C185" t="n">
+        <v>13.900176</v>
+      </c>
+      <c r="D185" t="n">
+        <v>96.41723399999999</v>
+      </c>
+      <c r="E185" t="n">
+        <v>81.70446099999999</v>
+      </c>
+      <c r="F185" t="n">
+        <v>133.544456</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B186" t="n">
+        <v>8.350685</v>
+      </c>
+      <c r="C186" t="n">
+        <v>14.789819</v>
+      </c>
+      <c r="D186" t="n">
+        <v>97.870126</v>
+      </c>
+      <c r="E186" t="n">
+        <v>83.032483</v>
+      </c>
+      <c r="F186" t="n">
+        <v>137.836237</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/ireland_gni_transparency_daily.xlsx
+++ b/output/Data and Chart Outputs/ireland_gni_transparency_daily.xlsx
@@ -157,6 +157,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Ireland gas entry flows (GNI) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -186,12 +187,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$186</f>
+              <f>'Chart'!$E$2:$E$210</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$186</f>
+              <f>'Chart'!$B$2:$B$210</f>
             </numRef>
           </val>
         </ser>
@@ -214,12 +215,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$186</f>
+              <f>'Chart'!$E$2:$E$210</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$186</f>
+              <f>'Chart'!$C$2:$C$210</f>
             </numRef>
           </val>
         </ser>
@@ -242,12 +243,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$186</f>
+              <f>'Chart'!$E$2:$E$210</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$186</f>
+              <f>'Chart'!$D$2:$D$210</f>
             </numRef>
           </val>
         </ser>
@@ -345,6 +346,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Ireland gas consumption by market sector (GNI) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -374,12 +376,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Consumption'!$E$2:$E$186</f>
+              <f>'Chart - Consumption'!$E$2:$E$210</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Consumption'!$B$2:$B$186</f>
+              <f>'Chart - Consumption'!$B$2:$B$210</f>
             </numRef>
           </val>
         </ser>
@@ -402,12 +404,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Consumption'!$E$2:$E$186</f>
+              <f>'Chart - Consumption'!$E$2:$E$210</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Consumption'!$C$2:$C$186</f>
+              <f>'Chart - Consumption'!$C$2:$C$210</f>
             </numRef>
           </val>
         </ser>
@@ -430,12 +432,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart - Consumption'!$E$2:$E$186</f>
+              <f>'Chart - Consumption'!$E$2:$E$210</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Consumption'!$D$2:$D$186</f>
+              <f>'Chart - Consumption'!$D$2:$D$210</f>
             </numRef>
           </val>
         </ser>
@@ -962,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E186"/>
+  <dimension ref="A1:E210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3240,6 +3242,9 @@
       <c r="C163" t="n">
         <v>0</v>
       </c>
+      <c r="D163" t="n">
+        <v>151.677778</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
@@ -3251,6 +3256,9 @@
       <c r="C164" t="n">
         <v>0</v>
       </c>
+      <c r="D164" t="n">
+        <v>182.477778</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
@@ -3262,6 +3270,9 @@
       <c r="C165" t="n">
         <v>0</v>
       </c>
+      <c r="D165" t="n">
+        <v>151.466667</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
@@ -3273,6 +3284,9 @@
       <c r="C166" t="n">
         <v>0</v>
       </c>
+      <c r="D166" t="n">
+        <v>0.01603</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
@@ -3306,9 +3320,6 @@
       <c r="C169" t="n">
         <v>0</v>
       </c>
-      <c r="D169" t="n">
-        <v>163.711111</v>
-      </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
@@ -3320,9 +3331,6 @@
       <c r="C170" t="n">
         <v>0</v>
       </c>
-      <c r="D170" t="n">
-        <v>149.322222</v>
-      </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n">
@@ -3334,9 +3342,6 @@
       <c r="C171" t="n">
         <v>0</v>
       </c>
-      <c r="D171" t="n">
-        <v>154.066667</v>
-      </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n">
@@ -3545,12 +3550,336 @@
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>141.777778</v>
+        <v>141.733333</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>Oct/26</t>
         </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B187" t="n">
+        <v>22.301663</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0</v>
+      </c>
+      <c r="D187" t="n">
+        <v>150.877778</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B188" t="n">
+        <v>22.153502</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" t="n">
+        <v>149.455556</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B189" t="n">
+        <v>21.830913</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0</v>
+      </c>
+      <c r="D189" t="n">
+        <v>128.311111</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B190" t="n">
+        <v>22.45492</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" t="n">
+        <v>167.455556</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B191" t="n">
+        <v>22.64377</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" t="n">
+        <v>204.786808</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B192" t="n">
+        <v>22.492491</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0</v>
+      </c>
+      <c r="D192" t="n">
+        <v>170.444444</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B193" t="n">
+        <v>22.518618</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0</v>
+      </c>
+      <c r="D193" t="n">
+        <v>162.844444</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B194" t="n">
+        <v>22.630946</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" t="n">
+        <v>126.744444</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B195" t="n">
+        <v>22.547728</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0</v>
+      </c>
+      <c r="D195" t="n">
+        <v>140.755556</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B196" t="n">
+        <v>22.489041</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0</v>
+      </c>
+      <c r="D196" t="n">
+        <v>155.333333</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B197" t="n">
+        <v>22.407528</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" t="n">
+        <v>161.577778</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B198" t="n">
+        <v>22.219688</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0</v>
+      </c>
+      <c r="D198" t="n">
+        <v>128.78</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B199" t="n">
+        <v>22.162275</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B200" t="n">
+        <v>22.140944</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B201" t="n">
+        <v>22.085235</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B202" t="n">
+        <v>22.083682</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B203" t="n">
+        <v>22.019985</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0</v>
+      </c>
+      <c r="D203" t="n">
+        <v>206.055556</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B204" t="n">
+        <v>22.052637</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0</v>
+      </c>
+      <c r="D204" t="n">
+        <v>219.45</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B205" t="n">
+        <v>22.036841</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0</v>
+      </c>
+      <c r="D205" t="n">
+        <v>166.025</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B206" t="n">
+        <v>21.988599</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0</v>
+      </c>
+      <c r="D206" t="n">
+        <v>204.591667</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B207" t="n">
+        <v>21.928376</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0</v>
+      </c>
+      <c r="D207" t="n">
+        <v>212.386111</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B208" t="n">
+        <v>21.822453</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0</v>
+      </c>
+      <c r="D208" t="n">
+        <v>187.494444</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B209" t="n">
+        <v>22.671769</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0</v>
+      </c>
+      <c r="D209" t="n">
+        <v>149.355556</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B210" t="n">
+        <v>21.700602</v>
+      </c>
+      <c r="C210" t="n">
+        <v>0</v>
+      </c>
+      <c r="D210" t="n">
+        <v>155.893333</v>
       </c>
     </row>
   </sheetData>
@@ -3565,7 +3894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E186"/>
+  <dimension ref="A1:E210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6189,10 +6518,10 @@
         <v>81.78750099999999</v>
       </c>
       <c r="C184" t="n">
-        <v>8.429243999999999</v>
+        <v>8.429319</v>
       </c>
       <c r="D184" t="n">
-        <v>15.025879</v>
+        <v>15.0257</v>
       </c>
     </row>
     <row r="185">
@@ -6206,7 +6535,7 @@
         <v>8.294691</v>
       </c>
       <c r="D185" t="n">
-        <v>13.900176</v>
+        <v>13.900095</v>
       </c>
     </row>
     <row r="186">
@@ -6217,15 +6546,351 @@
         <v>83.032483</v>
       </c>
       <c r="C186" t="n">
-        <v>8.350685</v>
+        <v>8.357726</v>
       </c>
       <c r="D186" t="n">
-        <v>14.789819</v>
+        <v>14.782822</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>Oct/26</t>
         </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B187" t="n">
+        <v>90.999495</v>
+      </c>
+      <c r="C187" t="n">
+        <v>7.832072999999999</v>
+      </c>
+      <c r="D187" t="n">
+        <v>15.350723</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B188" t="n">
+        <v>94.99970399999999</v>
+      </c>
+      <c r="C188" t="n">
+        <v>6.997965</v>
+      </c>
+      <c r="D188" t="n">
+        <v>14.916611</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B189" t="n">
+        <v>74.482467</v>
+      </c>
+      <c r="C189" t="n">
+        <v>6.201476</v>
+      </c>
+      <c r="D189" t="n">
+        <v>13.339281</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B190" t="n">
+        <v>111.623074</v>
+      </c>
+      <c r="C190" t="n">
+        <v>8.134162999999999</v>
+      </c>
+      <c r="D190" t="n">
+        <v>12.68999</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B191" t="n">
+        <v>135.137517</v>
+      </c>
+      <c r="C191" t="n">
+        <v>9.003622999999999</v>
+      </c>
+      <c r="D191" t="n">
+        <v>16.67447</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B192" t="n">
+        <v>101.273561</v>
+      </c>
+      <c r="C192" t="n">
+        <v>9.461335</v>
+      </c>
+      <c r="D192" t="n">
+        <v>20.515603</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B193" t="n">
+        <v>87.02923299999999</v>
+      </c>
+      <c r="C193" t="n">
+        <v>9.555655</v>
+      </c>
+      <c r="D193" t="n">
+        <v>25.095632</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B194" t="n">
+        <v>60.679134</v>
+      </c>
+      <c r="C194" t="n">
+        <v>8.399770999999999</v>
+      </c>
+      <c r="D194" t="n">
+        <v>20.725228</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B195" t="n">
+        <v>79.43892099999999</v>
+      </c>
+      <c r="C195" t="n">
+        <v>7.599343999999999</v>
+      </c>
+      <c r="D195" t="n">
+        <v>20.941022</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B196" t="n">
+        <v>89.59527799999999</v>
+      </c>
+      <c r="C196" t="n">
+        <v>6.760683999999999</v>
+      </c>
+      <c r="D196" t="n">
+        <v>20.050811</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B197" t="n">
+        <v>93.711945</v>
+      </c>
+      <c r="C197" t="n">
+        <v>8.204736</v>
+      </c>
+      <c r="D197" t="n">
+        <v>16.785138</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B198" t="n">
+        <v>68.005555</v>
+      </c>
+      <c r="C198" t="n">
+        <v>8.642337999999999</v>
+      </c>
+      <c r="D198" t="n">
+        <v>18.138671</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B199" t="n">
+        <v>68.026388</v>
+      </c>
+      <c r="C199" t="n">
+        <v>8.244427999999999</v>
+      </c>
+      <c r="D199" t="n">
+        <v>18.95804</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B200" t="n">
+        <v>127.767777</v>
+      </c>
+      <c r="C200" t="n">
+        <v>9.235229</v>
+      </c>
+      <c r="D200" t="n">
+        <v>21.087952</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B201" t="n">
+        <v>109.747222</v>
+      </c>
+      <c r="C201" t="n">
+        <v>8.946199999999999</v>
+      </c>
+      <c r="D201" t="n">
+        <v>25.225719</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B202" t="n">
+        <v>123.631668</v>
+      </c>
+      <c r="C202" t="n">
+        <v>8.18454</v>
+      </c>
+      <c r="D202" t="n">
+        <v>25.682893</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B203" t="n">
+        <v>128.103335</v>
+      </c>
+      <c r="C203" t="n">
+        <v>8.109551</v>
+      </c>
+      <c r="D203" t="n">
+        <v>26.450573</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B204" t="n">
+        <v>121.7025</v>
+      </c>
+      <c r="C204" t="n">
+        <v>10.084387</v>
+      </c>
+      <c r="D204" t="n">
+        <v>33.572503</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B205" t="n">
+        <v>83.945835</v>
+      </c>
+      <c r="C205" t="n">
+        <v>9.766048</v>
+      </c>
+      <c r="D205" t="n">
+        <v>28.213249</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B206" t="n">
+        <v>110.82111</v>
+      </c>
+      <c r="C206" t="n">
+        <v>9.974243999999999</v>
+      </c>
+      <c r="D206" t="n">
+        <v>32.691904</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B207" t="n">
+        <v>113.993873</v>
+      </c>
+      <c r="C207" t="n">
+        <v>10.179311</v>
+      </c>
+      <c r="D207" t="n">
+        <v>32.422137</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B208" t="n">
+        <v>88.94722299999999</v>
+      </c>
+      <c r="C208" t="n">
+        <v>10.106443</v>
+      </c>
+      <c r="D208" t="n">
+        <v>35.916835</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B209" t="n">
+        <v>70.267483</v>
+      </c>
+      <c r="C209" t="n">
+        <v>8.864737</v>
+      </c>
+      <c r="D209" t="n">
+        <v>32.443058</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B210" t="n">
+        <v>75.683021</v>
+      </c>
+      <c r="C210" t="n">
+        <v>7.504659999999999</v>
+      </c>
+      <c r="D210" t="n">
+        <v>31.043763</v>
       </c>
     </row>
   </sheetData>
@@ -6240,7 +6905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E186"/>
+  <dimension ref="A1:E210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8966,6 +9631,9 @@
       <c r="D163" t="n">
         <v>0</v>
       </c>
+      <c r="E163" t="n">
+        <v>151.677778</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="n">
@@ -8980,6 +9648,9 @@
       <c r="D164" t="n">
         <v>0</v>
       </c>
+      <c r="E164" t="n">
+        <v>182.477778</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="n">
@@ -8994,6 +9665,9 @@
       <c r="D165" t="n">
         <v>0</v>
       </c>
+      <c r="E165" t="n">
+        <v>151.466667</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="n">
@@ -9008,6 +9682,9 @@
       <c r="D166" t="n">
         <v>0</v>
       </c>
+      <c r="E166" t="n">
+        <v>0.01603</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="n">
@@ -9050,9 +9727,6 @@
       <c r="D169" t="n">
         <v>0</v>
       </c>
-      <c r="E169" t="n">
-        <v>163.711111</v>
-      </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="n">
@@ -9067,9 +9741,6 @@
       <c r="D170" t="n">
         <v>0</v>
       </c>
-      <c r="E170" t="n">
-        <v>149.322222</v>
-      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n">
@@ -9084,9 +9755,6 @@
       <c r="D171" t="n">
         <v>0</v>
       </c>
-      <c r="E171" t="n">
-        <v>154.066667</v>
-      </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="n">
@@ -9331,7 +9999,7 @@
         <v>46296</v>
       </c>
       <c r="B186" t="n">
-        <v>164.07468</v>
+        <v>164.030235</v>
       </c>
       <c r="C186" t="n">
         <v>22.166621</v>
@@ -9340,7 +10008,403 @@
         <v>0</v>
       </c>
       <c r="E186" t="n">
-        <v>141.777778</v>
+        <v>141.733333</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B187" t="n">
+        <v>173.462689</v>
+      </c>
+      <c r="C187" t="n">
+        <v>22.301663</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" t="n">
+        <v>150.877778</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B188" t="n">
+        <v>171.926344</v>
+      </c>
+      <c r="C188" t="n">
+        <v>22.153502</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="n">
+        <v>149.455556</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B189" t="n">
+        <v>150.440319</v>
+      </c>
+      <c r="C189" t="n">
+        <v>21.830913</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" t="n">
+        <v>128.311111</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B190" t="n">
+        <v>190.183063</v>
+      </c>
+      <c r="C190" t="n">
+        <v>22.45492</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" t="n">
+        <v>167.455556</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B191" t="n">
+        <v>227.703466</v>
+      </c>
+      <c r="C191" t="n">
+        <v>22.64377</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" t="n">
+        <v>204.786808</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B192" t="n">
+        <v>193.129381</v>
+      </c>
+      <c r="C192" t="n">
+        <v>22.492491</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" t="n">
+        <v>170.444444</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B193" t="n">
+        <v>185.56447</v>
+      </c>
+      <c r="C193" t="n">
+        <v>22.518618</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" t="n">
+        <v>162.844444</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B194" t="n">
+        <v>149.573899</v>
+      </c>
+      <c r="C194" t="n">
+        <v>22.630946</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="n">
+        <v>126.744444</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B195" t="n">
+        <v>163.507523</v>
+      </c>
+      <c r="C195" t="n">
+        <v>22.547728</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" t="n">
+        <v>140.755556</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B196" t="n">
+        <v>178.025175</v>
+      </c>
+      <c r="C196" t="n">
+        <v>22.489041</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="n">
+        <v>155.333333</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B197" t="n">
+        <v>184.184608</v>
+      </c>
+      <c r="C197" t="n">
+        <v>22.407528</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="n">
+        <v>161.577778</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B198" t="n">
+        <v>151.203325</v>
+      </c>
+      <c r="C198" t="n">
+        <v>22.219688</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="n">
+        <v>128.78</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B199" t="n">
+        <v>151.521268</v>
+      </c>
+      <c r="C199" t="n">
+        <v>22.162275</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B200" t="n">
+        <v>220.811123</v>
+      </c>
+      <c r="C200" t="n">
+        <v>22.140944</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B201" t="n">
+        <v>205.51015</v>
+      </c>
+      <c r="C201" t="n">
+        <v>22.085235</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B202" t="n">
+        <v>217.336452</v>
+      </c>
+      <c r="C202" t="n">
+        <v>22.083682</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B203" t="n">
+        <v>228.369594</v>
+      </c>
+      <c r="C203" t="n">
+        <v>22.019985</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" t="n">
+        <v>206.055556</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B204" t="n">
+        <v>241.800415</v>
+      </c>
+      <c r="C204" t="n">
+        <v>22.052637</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" t="n">
+        <v>219.45</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B205" t="n">
+        <v>188.430522</v>
+      </c>
+      <c r="C205" t="n">
+        <v>22.036841</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" t="n">
+        <v>166.025</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B206" t="n">
+        <v>226.833111</v>
+      </c>
+      <c r="C206" t="n">
+        <v>21.988599</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" t="n">
+        <v>204.591667</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B207" t="n">
+        <v>234.560838</v>
+      </c>
+      <c r="C207" t="n">
+        <v>21.928376</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0</v>
+      </c>
+      <c r="E207" t="n">
+        <v>212.386111</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B208" t="n">
+        <v>209.601363</v>
+      </c>
+      <c r="C208" t="n">
+        <v>21.822453</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>187.494444</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B209" t="n">
+        <v>172.343175</v>
+      </c>
+      <c r="C209" t="n">
+        <v>22.671769</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" t="n">
+        <v>149.355556</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B210" t="n">
+        <v>177.907624</v>
+      </c>
+      <c r="C210" t="n">
+        <v>21.700602</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" t="n">
+        <v>155.893333</v>
       </c>
     </row>
   </sheetData>
@@ -9354,7 +10418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F186"/>
+  <dimension ref="A1:F210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13034,19 +14098,19 @@
         <v>46294</v>
       </c>
       <c r="B184" t="n">
-        <v>8.429243999999999</v>
+        <v>8.429319</v>
       </c>
       <c r="C184" t="n">
-        <v>15.025879</v>
+        <v>15.0257</v>
       </c>
       <c r="D184" t="n">
-        <v>96.78906599999999</v>
+        <v>96.806276</v>
       </c>
       <c r="E184" t="n">
         <v>81.78750099999999</v>
       </c>
       <c r="F184" t="n">
-        <v>136.173511</v>
+        <v>136.190721</v>
       </c>
     </row>
     <row r="185">
@@ -13057,16 +14121,16 @@
         <v>8.294691</v>
       </c>
       <c r="C185" t="n">
-        <v>13.900176</v>
+        <v>13.900095</v>
       </c>
       <c r="D185" t="n">
-        <v>96.41723399999999</v>
+        <v>96.468357</v>
       </c>
       <c r="E185" t="n">
         <v>81.70446099999999</v>
       </c>
       <c r="F185" t="n">
-        <v>133.544456</v>
+        <v>133.595579</v>
       </c>
     </row>
     <row r="186">
@@ -13074,19 +14138,499 @@
         <v>46296</v>
       </c>
       <c r="B186" t="n">
-        <v>8.350685</v>
+        <v>8.357726</v>
       </c>
       <c r="C186" t="n">
-        <v>14.789819</v>
+        <v>14.782822</v>
       </c>
       <c r="D186" t="n">
-        <v>97.870126</v>
+        <v>97.85991199999999</v>
       </c>
       <c r="E186" t="n">
         <v>83.032483</v>
       </c>
       <c r="F186" t="n">
-        <v>137.836237</v>
+        <v>137.826023</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B187" t="n">
+        <v>7.832072999999999</v>
+      </c>
+      <c r="C187" t="n">
+        <v>15.350723</v>
+      </c>
+      <c r="D187" t="n">
+        <v>106.49884</v>
+      </c>
+      <c r="E187" t="n">
+        <v>90.999495</v>
+      </c>
+      <c r="F187" t="n">
+        <v>150.64884</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B188" t="n">
+        <v>6.997965</v>
+      </c>
+      <c r="C188" t="n">
+        <v>14.916611</v>
+      </c>
+      <c r="D188" t="n">
+        <v>109.722449</v>
+      </c>
+      <c r="E188" t="n">
+        <v>94.99970399999999</v>
+      </c>
+      <c r="F188" t="n">
+        <v>148.176616</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B189" t="n">
+        <v>6.201476</v>
+      </c>
+      <c r="C189" t="n">
+        <v>13.339281</v>
+      </c>
+      <c r="D189" t="n">
+        <v>87.856239</v>
+      </c>
+      <c r="E189" t="n">
+        <v>74.482467</v>
+      </c>
+      <c r="F189" t="n">
+        <v>126.29735</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B190" t="n">
+        <v>8.134162999999999</v>
+      </c>
+      <c r="C190" t="n">
+        <v>12.68999</v>
+      </c>
+      <c r="D190" t="n">
+        <v>125.484418</v>
+      </c>
+      <c r="E190" t="n">
+        <v>111.623074</v>
+      </c>
+      <c r="F190" t="n">
+        <v>166.192473</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B191" t="n">
+        <v>9.003622999999999</v>
+      </c>
+      <c r="C191" t="n">
+        <v>16.67447</v>
+      </c>
+      <c r="D191" t="n">
+        <v>150.194385</v>
+      </c>
+      <c r="E191" t="n">
+        <v>135.137517</v>
+      </c>
+      <c r="F191" t="n">
+        <v>196.412996</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B192" t="n">
+        <v>9.461335</v>
+      </c>
+      <c r="C192" t="n">
+        <v>20.515603</v>
+      </c>
+      <c r="D192" t="n">
+        <v>116.080665</v>
+      </c>
+      <c r="E192" t="n">
+        <v>101.273561</v>
+      </c>
+      <c r="F192" t="n">
+        <v>161.779553</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B193" t="n">
+        <v>9.555655</v>
+      </c>
+      <c r="C193" t="n">
+        <v>25.095632</v>
+      </c>
+      <c r="D193" t="n">
+        <v>101.845691</v>
+      </c>
+      <c r="E193" t="n">
+        <v>87.02923299999999</v>
+      </c>
+      <c r="F193" t="n">
+        <v>148.157358</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B194" t="n">
+        <v>8.399770999999999</v>
+      </c>
+      <c r="C194" t="n">
+        <v>20.725228</v>
+      </c>
+      <c r="D194" t="n">
+        <v>75.228398</v>
+      </c>
+      <c r="E194" t="n">
+        <v>60.679134</v>
+      </c>
+      <c r="F194" t="n">
+        <v>116.405342</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B195" t="n">
+        <v>7.599343999999999</v>
+      </c>
+      <c r="C195" t="n">
+        <v>20.941022</v>
+      </c>
+      <c r="D195" t="n">
+        <v>93.630532</v>
+      </c>
+      <c r="E195" t="n">
+        <v>79.43892099999999</v>
+      </c>
+      <c r="F195" t="n">
+        <v>135.099699</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B196" t="n">
+        <v>6.760683999999999</v>
+      </c>
+      <c r="C196" t="n">
+        <v>20.050811</v>
+      </c>
+      <c r="D196" t="n">
+        <v>102.911586</v>
+      </c>
+      <c r="E196" t="n">
+        <v>89.59527799999999</v>
+      </c>
+      <c r="F196" t="n">
+        <v>145.702142</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B197" t="n">
+        <v>8.204736</v>
+      </c>
+      <c r="C197" t="n">
+        <v>16.785138</v>
+      </c>
+      <c r="D197" t="n">
+        <v>107.183544</v>
+      </c>
+      <c r="E197" t="n">
+        <v>93.711945</v>
+      </c>
+      <c r="F197" t="n">
+        <v>152.845211</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B198" t="n">
+        <v>8.642337999999999</v>
+      </c>
+      <c r="C198" t="n">
+        <v>18.138671</v>
+      </c>
+      <c r="D198" t="n">
+        <v>81.63386799999999</v>
+      </c>
+      <c r="E198" t="n">
+        <v>68.005555</v>
+      </c>
+      <c r="F198" t="n">
+        <v>122.782757</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B199" t="n">
+        <v>8.244427999999999</v>
+      </c>
+      <c r="C199" t="n">
+        <v>18.95804</v>
+      </c>
+      <c r="D199" t="n">
+        <v>81.542424</v>
+      </c>
+      <c r="E199" t="n">
+        <v>68.026388</v>
+      </c>
+      <c r="F199" t="n">
+        <v>123.170202</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B200" t="n">
+        <v>9.235229</v>
+      </c>
+      <c r="C200" t="n">
+        <v>21.087952</v>
+      </c>
+      <c r="D200" t="n">
+        <v>142.967223</v>
+      </c>
+      <c r="E200" t="n">
+        <v>127.767777</v>
+      </c>
+      <c r="F200" t="n">
+        <v>186.116668</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B201" t="n">
+        <v>8.946199999999999</v>
+      </c>
+      <c r="C201" t="n">
+        <v>25.225719</v>
+      </c>
+      <c r="D201" t="n">
+        <v>125.016357</v>
+      </c>
+      <c r="E201" t="n">
+        <v>109.747222</v>
+      </c>
+      <c r="F201" t="n">
+        <v>170.57969</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B202" t="n">
+        <v>8.18454</v>
+      </c>
+      <c r="C202" t="n">
+        <v>25.682893</v>
+      </c>
+      <c r="D202" t="n">
+        <v>139.028323</v>
+      </c>
+      <c r="E202" t="n">
+        <v>123.631668</v>
+      </c>
+      <c r="F202" t="n">
+        <v>183.153323</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B203" t="n">
+        <v>8.109551</v>
+      </c>
+      <c r="C203" t="n">
+        <v>26.450573</v>
+      </c>
+      <c r="D203" t="n">
+        <v>143.659546</v>
+      </c>
+      <c r="E203" t="n">
+        <v>128.103335</v>
+      </c>
+      <c r="F203" t="n">
+        <v>190.095379</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B204" t="n">
+        <v>10.084387</v>
+      </c>
+      <c r="C204" t="n">
+        <v>33.572503</v>
+      </c>
+      <c r="D204" t="n">
+        <v>136.646094</v>
+      </c>
+      <c r="E204" t="n">
+        <v>121.7025</v>
+      </c>
+      <c r="F204" t="n">
+        <v>190.687761</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B205" t="n">
+        <v>9.766048</v>
+      </c>
+      <c r="C205" t="n">
+        <v>28.213249</v>
+      </c>
+      <c r="D205" t="n">
+        <v>98.93673699999999</v>
+      </c>
+      <c r="E205" t="n">
+        <v>83.945835</v>
+      </c>
+      <c r="F205" t="n">
+        <v>147.973126</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B206" t="n">
+        <v>9.974243999999999</v>
+      </c>
+      <c r="C206" t="n">
+        <v>32.691904</v>
+      </c>
+      <c r="D206" t="n">
+        <v>126.428304</v>
+      </c>
+      <c r="E206" t="n">
+        <v>110.82111</v>
+      </c>
+      <c r="F206" t="n">
+        <v>179.180249</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B207" t="n">
+        <v>10.179311</v>
+      </c>
+      <c r="C207" t="n">
+        <v>32.422137</v>
+      </c>
+      <c r="D207" t="n">
+        <v>129.360982</v>
+      </c>
+      <c r="E207" t="n">
+        <v>113.993873</v>
+      </c>
+      <c r="F207" t="n">
+        <v>187.13876</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B208" t="n">
+        <v>10.106443</v>
+      </c>
+      <c r="C208" t="n">
+        <v>35.916835</v>
+      </c>
+      <c r="D208" t="n">
+        <v>104.450255</v>
+      </c>
+      <c r="E208" t="n">
+        <v>88.94722299999999</v>
+      </c>
+      <c r="F208" t="n">
+        <v>158.343867</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B209" t="n">
+        <v>8.864737</v>
+      </c>
+      <c r="C209" t="n">
+        <v>32.443058</v>
+      </c>
+      <c r="D209" t="n">
+        <v>85.128794</v>
+      </c>
+      <c r="E209" t="n">
+        <v>70.267483</v>
+      </c>
+      <c r="F209" t="n">
+        <v>134.640461</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B210" t="n">
+        <v>7.504659999999999</v>
+      </c>
+      <c r="C210" t="n">
+        <v>31.043763</v>
+      </c>
+      <c r="D210" t="n">
+        <v>89.45820499999999</v>
+      </c>
+      <c r="E210" t="n">
+        <v>75.683021</v>
+      </c>
+      <c r="F210" t="n">
+        <v>137.051539</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/ireland_gni_transparency_daily.xlsx
+++ b/output/Data and Chart Outputs/ireland_gni_transparency_daily.xlsx
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>0.01603</v>
+        <v>160.3</v>
       </c>
     </row>
     <row r="167">
@@ -3298,6 +3298,9 @@
       <c r="C167" t="n">
         <v>0</v>
       </c>
+      <c r="D167" t="n">
+        <v>150.3</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
@@ -3309,6 +3312,9 @@
       <c r="C168" t="n">
         <v>0</v>
       </c>
+      <c r="D168" t="n">
+        <v>180.155556</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
@@ -3320,6 +3326,9 @@
       <c r="C169" t="n">
         <v>0</v>
       </c>
+      <c r="D169" t="n">
+        <v>163.711111</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
@@ -3331,6 +3340,9 @@
       <c r="C170" t="n">
         <v>0</v>
       </c>
+      <c r="D170" t="n">
+        <v>149.322222</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n">
@@ -3341,6 +3353,9 @@
       </c>
       <c r="C171" t="n">
         <v>0</v>
+      </c>
+      <c r="D171" t="n">
+        <v>154.066667</v>
       </c>
     </row>
     <row r="172">
@@ -3667,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="D194" t="n">
-        <v>126.744444</v>
+        <v>0.012674</v>
       </c>
     </row>
     <row r="195">
@@ -3680,9 +3695,6 @@
       <c r="C195" t="n">
         <v>0</v>
       </c>
-      <c r="D195" t="n">
-        <v>140.755556</v>
-      </c>
     </row>
     <row r="196">
       <c r="A196" s="3" t="n">
@@ -3736,6 +3748,9 @@
       <c r="C199" t="n">
         <v>0</v>
       </c>
+      <c r="D199" t="n">
+        <v>129.155556</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="3" t="n">
@@ -3747,6 +3762,9 @@
       <c r="C200" t="n">
         <v>0</v>
       </c>
+      <c r="D200" t="n">
+        <v>198.333333</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="3" t="n">
@@ -3758,6 +3776,9 @@
       <c r="C201" t="n">
         <v>0</v>
       </c>
+      <c r="D201" t="n">
+        <v>183.166667</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="n">
@@ -3768,6 +3789,9 @@
       </c>
       <c r="C202" t="n">
         <v>0</v>
+      </c>
+      <c r="D202" t="n">
+        <v>194.966667</v>
       </c>
     </row>
     <row r="203">
@@ -9683,7 +9707,7 @@
         <v>0</v>
       </c>
       <c r="E166" t="n">
-        <v>0.01603</v>
+        <v>160.3</v>
       </c>
     </row>
     <row r="167">
@@ -9699,6 +9723,9 @@
       <c r="D167" t="n">
         <v>0</v>
       </c>
+      <c r="E167" t="n">
+        <v>150.3</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="n">
@@ -9713,6 +9740,9 @@
       <c r="D168" t="n">
         <v>0</v>
       </c>
+      <c r="E168" t="n">
+        <v>180.155556</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n">
@@ -9727,6 +9757,9 @@
       <c r="D169" t="n">
         <v>0</v>
       </c>
+      <c r="E169" t="n">
+        <v>163.711111</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="n">
@@ -9741,6 +9774,9 @@
       <c r="D170" t="n">
         <v>0</v>
       </c>
+      <c r="E170" t="n">
+        <v>149.322222</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n">
@@ -9755,6 +9791,9 @@
       <c r="D171" t="n">
         <v>0</v>
       </c>
+      <c r="E171" t="n">
+        <v>154.066667</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="n">
@@ -10144,7 +10183,7 @@
         <v>0</v>
       </c>
       <c r="E194" t="n">
-        <v>126.744444</v>
+        <v>0.012674</v>
       </c>
     </row>
     <row r="195">
@@ -10160,9 +10199,6 @@
       <c r="D195" t="n">
         <v>0</v>
       </c>
-      <c r="E195" t="n">
-        <v>140.755556</v>
-      </c>
     </row>
     <row r="196">
       <c r="A196" s="4" t="n">
@@ -10228,6 +10264,9 @@
       <c r="D199" t="n">
         <v>0</v>
       </c>
+      <c r="E199" t="n">
+        <v>129.155556</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="n">
@@ -10242,6 +10281,9 @@
       <c r="D200" t="n">
         <v>0</v>
       </c>
+      <c r="E200" t="n">
+        <v>198.333333</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="n">
@@ -10256,6 +10298,9 @@
       <c r="D201" t="n">
         <v>0</v>
       </c>
+      <c r="E201" t="n">
+        <v>183.166667</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="n">
@@ -10269,6 +10314,9 @@
       </c>
       <c r="D202" t="n">
         <v>0</v>
+      </c>
+      <c r="E202" t="n">
+        <v>194.966667</v>
       </c>
     </row>
     <row r="203">
